--- a/_templates/Workpaper_Templates.xlsx
+++ b/_templates/Workpaper_Templates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fjmgt-my.sharepoint.com/personal/colby_kellersberger_fjmgt_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2168" documentId="8_{2AA950BE-A529-478E-BC2D-FFFCAC62050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36568684-9954-4A06-BE09-5324B691B546}"/>
+  <xr:revisionPtr revIDLastSave="2171" documentId="8_{2AA950BE-A529-478E-BC2D-FFFCAC62050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE48414E-45AA-488A-A1AC-6760534244EF}"/>
   <bookViews>
     <workbookView xWindow="3072" yWindow="1512" windowWidth="29772" windowHeight="22392" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -679,7 +679,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -880,6 +880,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF68925"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1728,10 +1734,6 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="36" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="34" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1759,6 +1761,24 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -1773,96 +1793,82 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="41" fillId="37" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2461,14 +2467,14 @@
   <sheetData>
     <row r="1" spans="2:20" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:20" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -2486,10 +2492,10 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="95"/>
+      <c r="C4" s="100"/>
       <c r="D4" s="102"/>
       <c r="E4" s="103"/>
       <c r="F4" s="104"/>
@@ -2502,10 +2508,10 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="107" t="s">
+      <c r="B5" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="105"/>
+      <c r="C5" s="95"/>
       <c r="D5" s="102"/>
       <c r="E5" s="103"/>
       <c r="F5" s="104"/>
@@ -2518,10 +2524,10 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="105" t="s">
+      <c r="B6" s="95" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="106"/>
+      <c r="C6" s="96"/>
       <c r="D6" s="102"/>
       <c r="E6" s="103"/>
       <c r="F6" s="104"/>
@@ -2557,50 +2563,50 @@
       <c r="B10" s="56">
         <v>1</v>
       </c>
-      <c r="C10" s="87"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="101"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="94"/>
       <c r="H10" s="24"/>
     </row>
     <row r="11" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56">
         <v>2</v>
       </c>
-      <c r="C11" s="87"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="100"/>
-      <c r="F11" s="101"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="94"/>
       <c r="H11" s="24"/>
     </row>
     <row r="12" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56">
         <v>3</v>
       </c>
-      <c r="C12" s="87"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="101"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="94"/>
       <c r="H12" s="24"/>
     </row>
     <row r="13" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="56">
         <v>4</v>
       </c>
-      <c r="C13" s="87"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="101"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="94"/>
       <c r="H13" s="24"/>
     </row>
     <row r="14" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="56">
         <v>5</v>
       </c>
-      <c r="C14" s="87"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="100"/>
-      <c r="F14" s="101"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="94"/>
       <c r="H14" s="24"/>
     </row>
     <row r="15" spans="2:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2624,36 +2630,36 @@
       <c r="B17" s="1"/>
       <c r="F17" s="65"/>
       <c r="G17" s="65"/>
-      <c r="H17" s="96" t="s">
+      <c r="H17" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
+      <c r="I17" s="101"/>
+      <c r="J17" s="101"/>
+      <c r="K17" s="101"/>
+      <c r="L17" s="101"/>
     </row>
     <row r="18" spans="2:14" s="31" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="86">
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="126"/>
+      <c r="G18" s="126"/>
+      <c r="H18" s="85">
         <v>1</v>
       </c>
-      <c r="I18" s="86">
+      <c r="I18" s="85">
         <v>2</v>
       </c>
-      <c r="J18" s="86">
+      <c r="J18" s="85">
         <v>3</v>
       </c>
-      <c r="K18" s="86">
+      <c r="K18" s="85">
         <v>4</v>
       </c>
-      <c r="L18" s="86">
+      <c r="L18" s="85">
         <v>5</v>
       </c>
       <c r="M18" s="17" t="s">
@@ -2665,24 +2671,24 @@
       <c r="B19" s="25">
         <v>1</v>
       </c>
-      <c r="C19" s="91"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="91"/>
-      <c r="H19" s="88" t="s">
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="89" t="s">
+      <c r="I19" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="J19" s="88" t="s">
+      <c r="J19" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="K19" s="88" t="s">
+      <c r="K19" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="L19" s="88" t="s">
+      <c r="L19" s="87" t="s">
         <v>50</v>
       </c>
       <c r="M19" s="33"/>
@@ -2691,12 +2697,12 @@
       <c r="B20" s="25">
         <v>2</v>
       </c>
-      <c r="C20" s="92"/>
-      <c r="D20" s="92"/>
-      <c r="E20" s="92"/>
-      <c r="F20" s="92"/>
-      <c r="G20" s="92"/>
-      <c r="H20" s="90"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="89"/>
       <c r="I20" s="21"/>
       <c r="J20" s="22"/>
       <c r="K20" s="23"/>
@@ -2707,12 +2713,12 @@
       <c r="B21" s="25">
         <v>3</v>
       </c>
-      <c r="C21" s="92"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="92"/>
-      <c r="G21" s="92"/>
-      <c r="H21" s="90"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="89"/>
       <c r="I21" s="21"/>
       <c r="J21" s="22"/>
       <c r="K21" s="23"/>
@@ -2723,12 +2729,12 @@
       <c r="B22" s="25">
         <v>4</v>
       </c>
-      <c r="C22" s="92"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="90"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="91"/>
+      <c r="H22" s="89"/>
       <c r="I22" s="21"/>
       <c r="J22" s="22"/>
       <c r="K22" s="23"/>
@@ -2739,12 +2745,12 @@
       <c r="B23" s="25">
         <v>5</v>
       </c>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="90"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="91"/>
+      <c r="H23" s="89"/>
       <c r="I23" s="21"/>
       <c r="J23" s="22"/>
       <c r="K23" s="23"/>
@@ -2755,12 +2761,12 @@
       <c r="B24" s="25">
         <v>6</v>
       </c>
-      <c r="C24" s="92"/>
-      <c r="D24" s="92"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="92"/>
-      <c r="G24" s="92"/>
-      <c r="H24" s="90"/>
+      <c r="C24" s="91"/>
+      <c r="D24" s="91"/>
+      <c r="E24" s="91"/>
+      <c r="F24" s="91"/>
+      <c r="G24" s="91"/>
+      <c r="H24" s="89"/>
       <c r="I24" s="21"/>
       <c r="J24" s="22"/>
       <c r="K24" s="23"/>
@@ -2771,12 +2777,12 @@
       <c r="B25" s="25">
         <v>7</v>
       </c>
-      <c r="C25" s="92"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="92"/>
-      <c r="G25" s="92"/>
-      <c r="H25" s="90"/>
+      <c r="C25" s="91"/>
+      <c r="D25" s="91"/>
+      <c r="E25" s="91"/>
+      <c r="F25" s="91"/>
+      <c r="G25" s="91"/>
+      <c r="H25" s="89"/>
       <c r="I25" s="21"/>
       <c r="J25" s="22"/>
       <c r="K25" s="23"/>
@@ -2787,12 +2793,12 @@
       <c r="B26" s="25">
         <v>8</v>
       </c>
-      <c r="C26" s="92"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="92"/>
-      <c r="G26" s="92"/>
-      <c r="H26" s="90"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="91"/>
+      <c r="G26" s="91"/>
+      <c r="H26" s="89"/>
       <c r="I26" s="21"/>
       <c r="J26" s="22"/>
       <c r="K26" s="23"/>
@@ -2803,12 +2809,12 @@
       <c r="B27" s="25">
         <v>9</v>
       </c>
-      <c r="C27" s="92"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="92"/>
-      <c r="F27" s="92"/>
-      <c r="G27" s="92"/>
-      <c r="H27" s="90"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="91"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="91"/>
+      <c r="H27" s="89"/>
       <c r="I27" s="21"/>
       <c r="J27" s="22"/>
       <c r="K27" s="23"/>
@@ -2819,12 +2825,12 @@
       <c r="B28" s="25">
         <v>10</v>
       </c>
-      <c r="C28" s="92"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
-      <c r="F28" s="92"/>
-      <c r="G28" s="92"/>
-      <c r="H28" s="90"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="91"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="91"/>
+      <c r="H28" s="89"/>
       <c r="I28" s="21"/>
       <c r="J28" s="22"/>
       <c r="K28" s="23"/>
@@ -2835,12 +2841,12 @@
       <c r="B29" s="25">
         <v>11</v>
       </c>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="92"/>
-      <c r="H29" s="90"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="91"/>
+      <c r="E29" s="91"/>
+      <c r="F29" s="91"/>
+      <c r="G29" s="91"/>
+      <c r="H29" s="89"/>
       <c r="I29" s="21"/>
       <c r="J29" s="22"/>
       <c r="K29" s="23"/>
@@ -2851,12 +2857,12 @@
       <c r="B30" s="25">
         <v>12</v>
       </c>
-      <c r="C30" s="92"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="92"/>
-      <c r="G30" s="92"/>
-      <c r="H30" s="90"/>
+      <c r="C30" s="91"/>
+      <c r="D30" s="91"/>
+      <c r="E30" s="91"/>
+      <c r="F30" s="91"/>
+      <c r="G30" s="91"/>
+      <c r="H30" s="89"/>
       <c r="I30" s="21"/>
       <c r="J30" s="22"/>
       <c r="K30" s="23"/>
@@ -2867,12 +2873,12 @@
       <c r="B31" s="25">
         <v>13</v>
       </c>
-      <c r="C31" s="92"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="92"/>
-      <c r="H31" s="90"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="91"/>
+      <c r="H31" s="89"/>
       <c r="I31" s="21"/>
       <c r="J31" s="22"/>
       <c r="K31" s="23"/>
@@ -2883,12 +2889,12 @@
       <c r="B32" s="25">
         <v>14</v>
       </c>
-      <c r="C32" s="92"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="92"/>
-      <c r="G32" s="92"/>
-      <c r="H32" s="90"/>
+      <c r="C32" s="91"/>
+      <c r="D32" s="91"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="91"/>
+      <c r="G32" s="91"/>
+      <c r="H32" s="89"/>
       <c r="I32" s="21"/>
       <c r="J32" s="22"/>
       <c r="K32" s="23"/>
@@ -2899,12 +2905,12 @@
       <c r="B33" s="25">
         <v>15</v>
       </c>
-      <c r="C33" s="92"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="92"/>
-      <c r="G33" s="92"/>
-      <c r="H33" s="90"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="89"/>
       <c r="I33" s="21"/>
       <c r="J33" s="22"/>
       <c r="K33" s="23"/>
@@ -2915,12 +2921,12 @@
       <c r="B34" s="25">
         <v>16</v>
       </c>
-      <c r="C34" s="92"/>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="92"/>
-      <c r="G34" s="92"/>
-      <c r="H34" s="90"/>
+      <c r="C34" s="91"/>
+      <c r="D34" s="91"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="91"/>
+      <c r="G34" s="91"/>
+      <c r="H34" s="89"/>
       <c r="I34" s="21"/>
       <c r="J34" s="22"/>
       <c r="K34" s="23"/>
@@ -2931,12 +2937,12 @@
       <c r="B35" s="25">
         <v>17</v>
       </c>
-      <c r="C35" s="92"/>
-      <c r="D35" s="92"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="92"/>
-      <c r="H35" s="90"/>
+      <c r="C35" s="91"/>
+      <c r="D35" s="91"/>
+      <c r="E35" s="91"/>
+      <c r="F35" s="91"/>
+      <c r="G35" s="91"/>
+      <c r="H35" s="89"/>
       <c r="I35" s="21"/>
       <c r="J35" s="22"/>
       <c r="K35" s="23"/>
@@ -2947,12 +2953,12 @@
       <c r="B36" s="25">
         <v>18</v>
       </c>
-      <c r="C36" s="92"/>
-      <c r="D36" s="92"/>
-      <c r="E36" s="92"/>
-      <c r="F36" s="92"/>
-      <c r="G36" s="92"/>
-      <c r="H36" s="90"/>
+      <c r="C36" s="91"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="91"/>
+      <c r="G36" s="91"/>
+      <c r="H36" s="89"/>
       <c r="I36" s="21"/>
       <c r="J36" s="22"/>
       <c r="K36" s="23"/>
@@ -2963,12 +2969,12 @@
       <c r="B37" s="25">
         <v>19</v>
       </c>
-      <c r="C37" s="92"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="90"/>
+      <c r="C37" s="91"/>
+      <c r="D37" s="91"/>
+      <c r="E37" s="91"/>
+      <c r="F37" s="91"/>
+      <c r="G37" s="91"/>
+      <c r="H37" s="89"/>
       <c r="I37" s="21"/>
       <c r="J37" s="22"/>
       <c r="K37" s="23"/>
@@ -2979,12 +2985,12 @@
       <c r="B38" s="25">
         <v>20</v>
       </c>
-      <c r="C38" s="92"/>
-      <c r="D38" s="92"/>
-      <c r="E38" s="92"/>
-      <c r="F38" s="92"/>
-      <c r="G38" s="92"/>
-      <c r="H38" s="90"/>
+      <c r="C38" s="91"/>
+      <c r="D38" s="91"/>
+      <c r="E38" s="91"/>
+      <c r="F38" s="91"/>
+      <c r="G38" s="91"/>
+      <c r="H38" s="89"/>
       <c r="I38" s="21"/>
       <c r="J38" s="22"/>
       <c r="K38" s="23"/>
@@ -2995,12 +3001,12 @@
       <c r="B39" s="25">
         <v>21</v>
       </c>
-      <c r="C39" s="92"/>
-      <c r="D39" s="92"/>
-      <c r="E39" s="92"/>
-      <c r="F39" s="92"/>
-      <c r="G39" s="92"/>
-      <c r="H39" s="90"/>
+      <c r="C39" s="91"/>
+      <c r="D39" s="91"/>
+      <c r="E39" s="91"/>
+      <c r="F39" s="91"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="89"/>
       <c r="I39" s="21"/>
       <c r="J39" s="22"/>
       <c r="K39" s="23"/>
@@ -3011,12 +3017,12 @@
       <c r="B40" s="25">
         <v>22</v>
       </c>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="92"/>
-      <c r="H40" s="90"/>
+      <c r="C40" s="91"/>
+      <c r="D40" s="91"/>
+      <c r="E40" s="91"/>
+      <c r="F40" s="91"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="89"/>
       <c r="I40" s="21"/>
       <c r="J40" s="22"/>
       <c r="K40" s="23"/>
@@ -3027,12 +3033,12 @@
       <c r="B41" s="25">
         <v>23</v>
       </c>
-      <c r="C41" s="92"/>
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="92"/>
-      <c r="H41" s="90"/>
+      <c r="C41" s="91"/>
+      <c r="D41" s="91"/>
+      <c r="E41" s="91"/>
+      <c r="F41" s="91"/>
+      <c r="G41" s="91"/>
+      <c r="H41" s="89"/>
       <c r="I41" s="21"/>
       <c r="J41" s="22"/>
       <c r="K41" s="23"/>
@@ -3043,12 +3049,12 @@
       <c r="B42" s="25">
         <v>24</v>
       </c>
-      <c r="C42" s="92"/>
-      <c r="D42" s="92"/>
-      <c r="E42" s="92"/>
-      <c r="F42" s="92"/>
-      <c r="G42" s="92"/>
-      <c r="H42" s="90"/>
+      <c r="C42" s="91"/>
+      <c r="D42" s="91"/>
+      <c r="E42" s="91"/>
+      <c r="F42" s="91"/>
+      <c r="G42" s="91"/>
+      <c r="H42" s="89"/>
       <c r="I42" s="21"/>
       <c r="J42" s="22"/>
       <c r="K42" s="23"/>
@@ -3059,12 +3065,12 @@
       <c r="B43" s="25">
         <v>25</v>
       </c>
-      <c r="C43" s="92"/>
-      <c r="D43" s="92"/>
-      <c r="E43" s="92"/>
-      <c r="F43" s="92"/>
-      <c r="G43" s="92"/>
-      <c r="H43" s="90"/>
+      <c r="C43" s="91"/>
+      <c r="D43" s="91"/>
+      <c r="E43" s="91"/>
+      <c r="F43" s="91"/>
+      <c r="G43" s="91"/>
+      <c r="H43" s="89"/>
       <c r="I43" s="21"/>
       <c r="J43" s="22"/>
       <c r="K43" s="23"/>
@@ -3119,27 +3125,27 @@
       <c r="G49" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H49" s="86">
+      <c r="H49" s="85">
         <v>1</v>
       </c>
-      <c r="I49" s="86">
+      <c r="I49" s="85">
         <v>2</v>
       </c>
-      <c r="J49" s="86">
+      <c r="J49" s="85">
         <v>3</v>
       </c>
-      <c r="K49" s="86">
+      <c r="K49" s="85">
         <v>4</v>
       </c>
-      <c r="L49" s="86">
+      <c r="L49" s="85">
         <v>5</v>
       </c>
     </row>
     <row r="50" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B50" s="58"/>
-      <c r="C50" s="99"/>
-      <c r="D50" s="100"/>
-      <c r="E50" s="101"/>
+      <c r="C50" s="92"/>
+      <c r="D50" s="93"/>
+      <c r="E50" s="94"/>
       <c r="G50" s="76" t="s">
         <v>50</v>
       </c>
@@ -3166,9 +3172,9 @@
     </row>
     <row r="51" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B51" s="58"/>
-      <c r="C51" s="99"/>
-      <c r="D51" s="100"/>
-      <c r="E51" s="101"/>
+      <c r="C51" s="92"/>
+      <c r="D51" s="93"/>
+      <c r="E51" s="94"/>
       <c r="G51" s="77" t="s">
         <v>45</v>
       </c>
@@ -3195,9 +3201,9 @@
     </row>
     <row r="52" spans="2:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B52" s="58"/>
-      <c r="C52" s="99"/>
-      <c r="D52" s="100"/>
-      <c r="E52" s="101"/>
+      <c r="C52" s="92"/>
+      <c r="D52" s="93"/>
+      <c r="E52" s="94"/>
       <c r="G52" s="78"/>
       <c r="H52" s="79" t="str">
         <f t="shared" ref="H52:L55" si="1">_xlfn.LET(_xlpm.x, COUNTIF(H$19:H$43, $G52), IF(_xlpm.x=0, "", _xlpm.x))</f>
@@ -3297,11 +3303,6 @@
     <row r="61" spans="2:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="H17:L17"/>
@@ -3313,6 +3314,11 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3344,14 +3350,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:21" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -3371,10 +3377,10 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="110" t="s">
+      <c r="B4" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="111"/>
+      <c r="C4" s="106"/>
       <c r="D4" s="102"/>
       <c r="E4" s="103"/>
       <c r="F4" s="104"/>
@@ -3388,10 +3394,10 @@
       <c r="U4" s="2"/>
     </row>
     <row r="5" spans="2:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="110" t="s">
+      <c r="B5" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="111"/>
+      <c r="C5" s="106"/>
       <c r="D5" s="102"/>
       <c r="E5" s="103"/>
       <c r="F5" s="104"/>
@@ -3443,45 +3449,45 @@
     <row r="10" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="56"/>
       <c r="C10" s="57"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="101"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="94"/>
       <c r="H10" s="24"/>
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56"/>
       <c r="C11" s="57"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="100"/>
-      <c r="F11" s="101"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="94"/>
       <c r="H11" s="24"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56"/>
       <c r="C12" s="57"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="101"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="94"/>
       <c r="H12" s="24"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="56"/>
       <c r="C13" s="57"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="101"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="94"/>
       <c r="H13" s="24"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="56"/>
       <c r="C14" s="57"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="100"/>
-      <c r="F14" s="101"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="94"/>
       <c r="H14" s="24"/>
       <c r="N14" s="14"/>
     </row>
@@ -3518,25 +3524,25 @@
     </row>
     <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="58"/>
-      <c r="C18" s="99"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="101"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="94"/>
       <c r="H18" s="24"/>
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="58"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="100"/>
-      <c r="E19" s="101"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="94"/>
       <c r="H19" s="24"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="58"/>
-      <c r="C20" s="99"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="101"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="94"/>
       <c r="H20" s="24"/>
       <c r="N20" s="14"/>
     </row>
@@ -3580,11 +3586,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:F5"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D12:F12"/>
@@ -3593,6 +3594,11 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3624,14 +3630,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -3651,19 +3657,19 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="110" t="s">
+      <c r="B4" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="111"/>
+      <c r="C4" s="106"/>
       <c r="D4" s="102"/>
       <c r="E4" s="103"/>
       <c r="F4" s="104"/>
     </row>
     <row r="5" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="110" t="s">
+      <c r="B5" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="111"/>
+      <c r="C5" s="106"/>
       <c r="D5" s="102"/>
       <c r="E5" s="103"/>
       <c r="F5" s="104"/>
@@ -3700,45 +3706,45 @@
     <row r="10" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="56"/>
       <c r="C10" s="57"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="101"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="94"/>
       <c r="H10" s="24"/>
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56"/>
       <c r="C11" s="57"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="100"/>
-      <c r="F11" s="101"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="94"/>
       <c r="H11" s="24"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56"/>
       <c r="C12" s="57"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="101"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="94"/>
       <c r="H12" s="24"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B13" s="56"/>
       <c r="C13" s="57"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="101"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="94"/>
       <c r="H13" s="24"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B14" s="56"/>
       <c r="C14" s="57"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="100"/>
-      <c r="F14" s="101"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="94"/>
       <c r="H14" s="24"/>
       <c r="N14" s="14"/>
     </row>
@@ -3775,25 +3781,25 @@
     </row>
     <row r="18" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="58"/>
-      <c r="C18" s="99"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="101"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="94"/>
       <c r="H18" s="24"/>
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B19" s="58"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="100"/>
-      <c r="E19" s="101"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="94"/>
       <c r="H19" s="24"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="21" x14ac:dyDescent="0.3">
       <c r="B20" s="58"/>
-      <c r="C20" s="99"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="101"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="94"/>
       <c r="H20" s="24"/>
       <c r="N20" s="14"/>
     </row>
@@ -3827,6 +3833,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D12:F12"/>
@@ -3835,11 +3846,6 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3860,36 +3866,36 @@
     <row r="3" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="110" t="s">
+      <c r="B5" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="111"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="118"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="109"/>
     </row>
     <row r="6" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="119" t="s">
+      <c r="B6" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="119"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="117"/>
-      <c r="J6" s="118"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="109"/>
     </row>
     <row r="7" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="105" t="s">
+      <c r="B7" s="95" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="105"/>
+      <c r="C7" s="95"/>
       <c r="D7" s="102"/>
       <c r="E7" s="103"/>
       <c r="F7" s="103"/>
@@ -3909,7 +3915,7 @@
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="97"/>
+      <c r="B11" s="114"/>
       <c r="C11" s="115"/>
       <c r="D11" s="115"/>
       <c r="E11" s="115"/>
@@ -3917,7 +3923,7 @@
       <c r="G11" s="115"/>
       <c r="H11" s="115"/>
       <c r="I11" s="115"/>
-      <c r="J11" s="98"/>
+      <c r="J11" s="116"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="14"/>
@@ -3931,7 +3937,7 @@
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="97"/>
+      <c r="B14" s="114"/>
       <c r="C14" s="115"/>
       <c r="D14" s="115"/>
       <c r="E14" s="115"/>
@@ -3939,7 +3945,7 @@
       <c r="G14" s="115"/>
       <c r="H14" s="115"/>
       <c r="I14" s="115"/>
-      <c r="J14" s="98"/>
+      <c r="J14" s="116"/>
     </row>
     <row r="16" spans="2:10" ht="18" x14ac:dyDescent="0.35">
       <c r="B16" s="61" t="s">
@@ -3947,7 +3953,7 @@
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="97"/>
+      <c r="B17" s="114"/>
       <c r="C17" s="115"/>
       <c r="D17" s="115"/>
       <c r="E17" s="115"/>
@@ -3955,7 +3961,7 @@
       <c r="G17" s="115"/>
       <c r="H17" s="115"/>
       <c r="I17" s="115"/>
-      <c r="J17" s="98"/>
+      <c r="J17" s="116"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="54"/>
@@ -3972,7 +3978,7 @@
       <c r="E19" s="54"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="97"/>
+      <c r="B20" s="114"/>
       <c r="C20" s="115"/>
       <c r="D20" s="115"/>
       <c r="E20" s="115"/>
@@ -3980,7 +3986,7 @@
       <c r="G20" s="115"/>
       <c r="H20" s="115"/>
       <c r="I20" s="115"/>
-      <c r="J20" s="98"/>
+      <c r="J20" s="116"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="14"/>
@@ -3997,7 +4003,7 @@
       <c r="E22" s="14"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="97"/>
+      <c r="B23" s="114"/>
       <c r="C23" s="115"/>
       <c r="D23" s="115"/>
       <c r="E23" s="115"/>
@@ -4005,7 +4011,7 @@
       <c r="G23" s="115"/>
       <c r="H23" s="115"/>
       <c r="I23" s="115"/>
-      <c r="J23" s="98"/>
+      <c r="J23" s="116"/>
     </row>
     <row r="25" spans="2:10" ht="21" x14ac:dyDescent="0.3">
       <c r="B25" s="45" t="s">
@@ -4022,30 +4028,30 @@
     </row>
     <row r="27" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B27" s="64"/>
-      <c r="C27" s="112"/>
-      <c r="D27" s="113"/>
-      <c r="E27" s="113"/>
-      <c r="F27" s="113"/>
-      <c r="G27" s="113"/>
-      <c r="H27" s="114"/>
+      <c r="C27" s="111"/>
+      <c r="D27" s="112"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="113"/>
     </row>
     <row r="28" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B28" s="64"/>
-      <c r="C28" s="112"/>
-      <c r="D28" s="113"/>
-      <c r="E28" s="113"/>
-      <c r="F28" s="113"/>
-      <c r="G28" s="113"/>
-      <c r="H28" s="114"/>
+      <c r="C28" s="111"/>
+      <c r="D28" s="112"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="112"/>
+      <c r="H28" s="113"/>
     </row>
     <row r="29" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B29" s="64"/>
-      <c r="C29" s="99"/>
-      <c r="D29" s="100"/>
-      <c r="E29" s="100"/>
-      <c r="F29" s="100"/>
-      <c r="G29" s="100"/>
-      <c r="H29" s="101"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="93"/>
+      <c r="E29" s="93"/>
+      <c r="F29" s="93"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="94"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="8"/>
@@ -4057,12 +4063,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:J7"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="B11:J11"/>
@@ -4071,6 +4071,12 @@
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="B23:J23"/>
     <mergeCell ref="C27:H27"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4103,14 +4109,14 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -4130,12 +4136,12 @@
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="120" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="126"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="123"/>
       <c r="G4" s="65"/>
       <c r="H4" s="59"/>
       <c r="I4" s="59"/>
@@ -4166,9 +4172,9 @@
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="54"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="122"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="119"/>
       <c r="G7" s="65"/>
     </row>
     <row r="9" spans="2:21" ht="21" x14ac:dyDescent="0.3">
@@ -4178,9 +4184,9 @@
       <c r="C9" s="51"/>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C10" s="120"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="122"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="119"/>
       <c r="G10" s="65"/>
     </row>
     <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.3">
@@ -4189,9 +4195,9 @@
       </c>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C13" s="120"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="122"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="119"/>
       <c r="G13" s="65"/>
     </row>
     <row r="15" spans="2:21" ht="21" x14ac:dyDescent="0.3">
@@ -4200,9 +4206,9 @@
       </c>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C16" s="120"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="122"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="119"/>
       <c r="G16" s="65"/>
     </row>
     <row r="18" spans="2:5" ht="21" x14ac:dyDescent="0.3">
@@ -4314,24 +4320,24 @@
       <c r="B3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="109" t="s">
+      <c r="C3" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="109"/>
-      <c r="F3" s="108" t="s">
+      <c r="D3" s="124"/>
+      <c r="F3" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
     </row>
     <row r="4" spans="2:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="109"/>
+      <c r="D4" s="124"/>
       <c r="F4" s="36" t="s">
         <v>8</v>
       </c>
@@ -4341,10 +4347,10 @@
       <c r="B5" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="109" t="s">
+      <c r="C5" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="109"/>
+      <c r="D5" s="124"/>
       <c r="F5" s="36" t="s">
         <v>11</v>
       </c>
@@ -4354,10 +4360,10 @@
       <c r="B6" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="109" t="s">
+      <c r="C6" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="109"/>
+      <c r="D6" s="124"/>
       <c r="F6" s="37" t="s">
         <v>14</v>
       </c>
@@ -4367,10 +4373,10 @@
       <c r="B7" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109" t="s">
+      <c r="C7" s="124" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="109"/>
+      <c r="D7" s="124"/>
       <c r="F7" s="35" t="s">
         <v>17</v>
       </c>
@@ -4380,46 +4386,46 @@
       <c r="B8" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="109" t="s">
+      <c r="C8" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="109"/>
+      <c r="D8" s="124"/>
     </row>
     <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="109" t="s">
+      <c r="C9" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="109"/>
+      <c r="D9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="109" t="s">
+      <c r="C10" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="109"/>
+      <c r="D10" s="124"/>
     </row>
     <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="109" t="s">
+      <c r="C11" s="124" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="109"/>
+      <c r="D11" s="124"/>
     </row>
     <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="109" t="s">
+      <c r="C12" s="124" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="109"/>
+      <c r="D12" s="124"/>
     </row>
     <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="42"/>
@@ -4429,27 +4435,32 @@
       <c r="B14" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="109" t="s">
+      <c r="C14" s="124" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="109"/>
+      <c r="D14" s="124"/>
     </row>
     <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="41"/>
-      <c r="C15" s="109"/>
-      <c r="D15" s="109"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="109" t="s">
+      <c r="C16" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="109"/>
+      <c r="D16" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
@@ -4459,17 +4470,49 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
+    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F6BF0C1AE5C4B149A9D2AD89D2837366" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="26a77736960804fb0d99dc8dd7184fdb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="c596204b-3c01-4828-83dd-c39c80911371" xmlns:ns3="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94048c9244edca77c34ed05855514cda" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4741,44 +4784,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
-    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24C080E9-4052-4FFB-9585-503A5ED8519B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4796,30 +4828,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>